--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_174_R18.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_174_R18.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3521</v>
+        <v>4.6291</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5445</v>
+        <v>4.8551</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1924</v>
+        <v>-0.226</v>
       </c>
       <c r="G2" t="n">
         <v>4.7095</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.3666</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9709</v>
+        <v>-0.6603</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3273</v>
+        <v>0.2937</v>
       </c>
       <c r="V2" t="n">
         <v>1.214</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5925</v>
+        <v>3.1378</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3442</v>
+        <v>1.9903</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2484</v>
+        <v>1.1476</v>
       </c>
       <c r="G3" t="n">
         <v>0.7677</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8764</v>
+        <v>0.4217</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3541</v>
+        <v>0.0002</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5223</v>
+        <v>0.4215</v>
       </c>
       <c r="V3" t="n">
         <v>0.7886</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4303</v>
+        <v>2.9452</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2714</v>
+        <v>3.456</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1589</v>
+        <v>-0.5108</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0597</v>
+        <v>-0.5407</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2654</v>
+        <v>-1.8222</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3251</v>
+        <v>1.2815</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1281</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7968</v>
+        <v>-1.2534</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3312</v>
+        <v>2.2317</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0683</v>
+        <v>-1.519</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0622</v>
+        <v>-0.5688</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9939</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1387</v>
+        <v>-1.1224</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4629</v>
+        <v>-0.507</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3242</v>
+        <v>-0.6155</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5361</v>
+        <v>3.2166</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>3.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1407</v>
+        <v>2.0224</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8531</v>
+        <v>0.9307</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7124</v>
+        <v>1.0917</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5407</v>
+        <v>1.0597</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8222</v>
+        <v>-0.2654</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2815</v>
+        <v>1.3251</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9782999999999999</v>
+        <v>1.1281</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2534</v>
+        <v>0.7968</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2317</v>
+        <v>0.3312</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.519</v>
+        <v>-0.0683</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5688</v>
+        <v>-1.0622</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9500999999999999</v>
+        <v>0.9939</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.2693</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1098</v>
+        <v>0.1221</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8171</v>
+        <v>-0.3914</v>
       </c>
       <c r="V5" t="n">
-        <v>3.2166</v>
+        <v>0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2166</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2909</v>
+        <v>1.8615</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5483</v>
+        <v>1.6229</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7427</v>
+        <v>0.2386</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7301</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3974</v>
+        <v>0.968</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3383</v>
+        <v>0.4129</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0592</v>
+        <v>0.5551</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7804</v>
+        <v>1.1091</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2437</v>
+        <v>2.3489</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4633</v>
+        <v>-1.2398</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2031</v>
+        <v>1.1902</v>
       </c>
       <c r="H7" t="n">
-        <v>1.54</v>
+        <v>-0.8475</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7431</v>
+        <v>2.0377</v>
       </c>
       <c r="J7" t="n">
-        <v>3.281</v>
+        <v>2.5124</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9193</v>
+        <v>-0.1107</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3618</v>
+        <v>2.6231</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.4842</v>
+        <v>-1.3222</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3792</v>
+        <v>-0.7369</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.1049</v>
+        <v>-0.5854</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.3195</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3195</v>
+        <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1253</v>
+        <v>-0.7923</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1404</v>
+        <v>-0.4676</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9849</v>
+        <v>-0.3246</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1418</v>
+        <v>-1.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2836</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.9805</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9204</v>
+        <v>0.1718</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.307</v>
+        <v>0.8087</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1902</v>
+        <v>-1.1175</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8475</v>
+        <v>0.2746</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0377</v>
+        <v>-1.3921</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5124</v>
+        <v>0.5405</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1107</v>
+        <v>0.3501</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6231</v>
+        <v>0.1904</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3222</v>
+        <v>-1.658</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7369</v>
+        <v>-0.0755</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5854</v>
+        <v>-1.5825</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5515</v>
+        <v>2.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.288</v>
+        <v>-0.116</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8962</v>
+        <v>0.2008</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3918</v>
+        <v>-0.3167</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6083</v>
+        <v>1.7501</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5361</v>
+        <v>1.7501</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0035</v>
+        <v>0.8621</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6106</v>
+        <v>1.7287</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6071</v>
+        <v>-0.8666</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1175</v>
+        <v>-0.2031</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2746</v>
+        <v>1.54</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3921</v>
+        <v>-1.7431</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5405</v>
+        <v>3.281</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3501</v>
+        <v>1.9193</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1904</v>
+        <v>1.3618</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.658</v>
+        <v>-3.4842</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0755</v>
+        <v>-0.3792</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5825</v>
+        <v>-3.1049</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7834</v>
+        <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1</v>
+        <v>1.207</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5816</v>
+        <v>0.6253</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5184</v>
+        <v>0.5816</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7501</v>
+        <v>-0.1418</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7501</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7975</v>
+        <v>-1.5376</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0834</v>
+        <v>-0.8907</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7141</v>
+        <v>-0.6469</v>
       </c>
       <c r="G10" t="n">
         <v>0.7764</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9656</v>
+        <v>-0.7057</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6721</v>
+        <v>-0.4795</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2934</v>
+        <v>-0.2262</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6083</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5075</v>
+        <v>-2.3218</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4648</v>
+        <v>-1.6824</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0427</v>
+        <v>-0.6394</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6586</v>
@@ -1312,13 +1312,13 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0086</v>
+        <v>0.177</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8804</v>
+        <v>-0.098</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1283</v>
+        <v>0.275</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6786</v>
+        <v>-2.7281</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2313</v>
+        <v>-3.4489</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5527</v>
+        <v>0.7208</v>
       </c>
       <c r="G12" t="n">
         <v>-4.345</v>
@@ -1390,13 +1390,13 @@
         <v>2.5515</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7252999999999999</v>
+        <v>0.2251</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6563</v>
+        <v>0.1261</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.2132</v>
+        <v>10.9602</v>
       </c>
       <c r="E13" t="n">
-        <v>10.3355</v>
+        <v>11.0824</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1220999999999999</v>
+        <v>-0.1221000000000002</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0915</v>
@@ -1468,13 +1468,13 @@
         <v>22.0356</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.120199999999999</v>
+        <v>-0.3735000000000003</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4716</v>
+        <v>-0.7250000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3514999999999999</v>
+        <v>0.3516</v>
       </c>
       <c r="V13" t="n">
         <v>4.147</v>
@@ -1483,7 +1483,7 @@
         <v>9.1448</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.997800000000001</v>
+        <v>-4.9978</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0449</v>
+        <v>7.9035</v>
       </c>
       <c r="E14" t="n">
-        <v>8.2361</v>
+        <v>8.825900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1912</v>
+        <v>-0.9224</v>
       </c>
       <c r="G14" t="n">
         <v>5.8499</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5008</v>
+        <v>0.3578</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4991</v>
+        <v>0.0907</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0018</v>
+        <v>0.2671</v>
       </c>
       <c r="V14" t="n">
         <v>0.5361</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1716</v>
+        <v>5.2578</v>
       </c>
       <c r="E15" t="n">
-        <v>3.867</v>
+        <v>3.2772</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3046</v>
+        <v>1.9806</v>
       </c>
       <c r="G15" t="n">
         <v>3.9541</v>
@@ -1624,13 +1624,13 @@
         <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3024</v>
+        <v>1.3886</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8496</v>
+        <v>0.2598</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4528</v>
+        <v>1.1288</v>
       </c>
       <c r="V15" t="n">
         <v>2.0026</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4415</v>
+        <v>0.6603</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5393</v>
+        <v>1.6573</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0978</v>
+        <v>-0.9969</v>
       </c>
       <c r="G16" t="n">
         <v>0.4899</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1656</v>
+        <v>0.3844</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2794</v>
+        <v>0.3973</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1138</v>
+        <v>-0.013</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6778999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>D. MOTIEJUNAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1027</v>
+        <v>-1.1039</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8159</v>
+        <v>-1.6309</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9187</v>
+        <v>0.527</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2616</v>
+        <v>1.2356</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9328</v>
+        <v>2.042</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1945</v>
+        <v>-0.8063</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6291</v>
+        <v>1.6501</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3983</v>
+        <v>1.6133</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2308</v>
+        <v>0.0368</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8907</v>
+        <v>-0.4144</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4655</v>
+        <v>0.4287</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4252</v>
+        <v>-0.8431</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3917</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0145</v>
+        <v>0.3047</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1019</v>
+        <v>-0.1729</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1164</v>
+        <v>0.4775</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>-0.7886</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6083</v>
+        <v>-0.7886</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MOTIEJUNAS</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.558</v>
+        <v>-1.1084</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7489</v>
+        <v>0.4621</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1909</v>
+        <v>-1.5705</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2356</v>
+        <v>-0.2616</v>
       </c>
       <c r="H18" t="n">
-        <v>2.042</v>
+        <v>0.9328</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8063</v>
+        <v>-1.1945</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6501</v>
+        <v>1.6291</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6133</v>
+        <v>1.3983</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0368</v>
+        <v>0.2308</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4144</v>
+        <v>-1.8907</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4287</v>
+        <v>-0.4655</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8431</v>
+        <v>-1.4252</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8556</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1494</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2908</v>
+        <v>-0.4558</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1415</v>
+        <v>0.4646</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7886</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7886</v>
+        <v>1.6083</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. DOS SANTOS</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.003</v>
+        <v>-1.2292</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8391</v>
+        <v>1.4894</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1639</v>
+        <v>-2.7185</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3702</v>
+        <v>1.0097</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6938</v>
+        <v>-0.4658</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6764</v>
+        <v>1.4755</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6229</v>
+        <v>3.8397</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.3256</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.6229</v>
+        <v>4.1654</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7473</v>
+        <v>-2.8301</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6938</v>
+        <v>-0.1401</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0535</v>
+        <v>-2.6899</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3286</v>
+        <v>0.3695</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2161</v>
+        <v>-0.1727</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1125</v>
+        <v>0.5421</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>Y. DOS SANTOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2514</v>
+        <v>-1.8178</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7816</v>
+        <v>-1.7211</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0331</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0097</v>
+        <v>-2.3702</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4658</v>
+        <v>-0.6938</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4755</v>
+        <v>-1.6764</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8397</v>
+        <v>-1.6229</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3256</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>4.1654</v>
+        <v>-1.6229</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8301</v>
+        <v>-0.7473</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1401</v>
+        <v>-0.6938</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.6899</v>
+        <v>-0.0535</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6528</v>
+        <v>-0.1434</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8804</v>
+        <v>-0.0982</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2276</v>
+        <v>-0.0452</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7943</v>
+        <v>-2.8108</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8673</v>
+        <v>-2.7493</v>
       </c>
       <c r="F21" t="n">
-        <v>0.073</v>
+        <v>-0.0614</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8231000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0228</v>
+        <v>-0.0393</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1265</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7886</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.734</v>
+        <v>-4.4354</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6087</v>
+        <v>-4.1985</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1253</v>
+        <v>-0.2369</v>
       </c>
       <c r="G22" t="n">
         <v>-3.5573</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0552</v>
+        <v>0.3539</v>
       </c>
       <c r="T22" t="n">
-        <v>0.767</v>
+        <v>0.1772</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2882</v>
+        <v>0.1766</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9272</v>
+        <v>-4.9003</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7199</v>
+        <v>-4.2161</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2073</v>
+        <v>-0.6842</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0058</v>
+        <v>-1.4298</v>
       </c>
       <c r="H23" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.4896</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0778</v>
+        <v>-0.9402</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0478</v>
+        <v>-0.2573</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2318</v>
+        <v>0.1008</v>
       </c>
       <c r="L23" t="n">
-        <v>0.184</v>
+        <v>-0.3581</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9581</v>
+        <v>-1.1725</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3038</v>
+        <v>-0.5904</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.2618</v>
+        <v>-0.5821</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6959</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0606</v>
+        <v>-0.2232</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4876</v>
+        <v>-0.4795</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.427</v>
+        <v>0.2563</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5008</v>
+        <v>-5.0566</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.334</v>
+        <v>-1.0737</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1668</v>
+        <v>-3.9828</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4298</v>
+        <v>-2.0058</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4896</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9402</v>
+        <v>-2.0778</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2573</v>
+        <v>-0.0478</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1008</v>
+        <v>-0.2318</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3581</v>
+        <v>0.184</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1725</v>
+        <v>-1.9581</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5904</v>
+        <v>0.3038</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5821</v>
+        <v>-2.2618</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.2473</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8237</v>
+        <v>-0.0688</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5975</v>
+        <v>0.1338</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2262</v>
+        <v>-0.2025</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.2134</v>
+        <v>-8.640799999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1220000000000017</v>
+        <v>0.1223000000000014</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.3356</v>
+        <v>-8.762699999999999</v>
       </c>
       <c r="G25" t="n">
         <v>2.091400000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>3.1453</v>
+        <v>3.145300000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-1.0539</v>
@@ -2404,13 +2404,13 @@
         <v>12.7575</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1202</v>
+        <v>2.693</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3516000000000002</v>
+        <v>-0.3517</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4717</v>
+        <v>3.0444</v>
       </c>
       <c r="V25" t="n">
         <v>-4.146999999999999</v>
